--- a/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_UserSatisfaction_CDF_3MethodCompare.xlsx
+++ b/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_UserSatisfaction_CDF_3MethodCompare.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="466" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1398" uniqueCount="17">
   <si>
     <t>method</t>
   </si>

--- a/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_UserSatisfaction_CDF_3MethodCompare.xlsx
+++ b/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U50_P03S49_UserSatisfaction_CDF_3MethodCompare.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1398" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2330" uniqueCount="19">
   <si>
     <t>method</t>
   </si>
@@ -66,6 +66,12 @@
   <si>
     <t>max_satisfaction</t>
   </si>
+  <si>
+    <t>Only HBR</t>
+  </si>
+  <si>
+    <t>EABR</t>
+  </si>
 </sst>
 </file>
 
@@ -113,12 +119,12 @@
   <dimension ref="A1:F148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.21875" customWidth="true"/>
-    <col min="2" max="2" width="14.88671875" customWidth="true"/>
-    <col min="3" max="3" width="13.5546875" customWidth="true"/>
-    <col min="4" max="4" width="18.5546875" customWidth="true"/>
-    <col min="5" max="5" width="7.21875" customWidth="true"/>
-    <col min="6" max="6" width="13.5546875" customWidth="true"/>
+    <col min="1" max="1" width="9.28515625" customWidth="true"/>
+    <col min="2" max="2" width="16.140625" customWidth="true"/>
+    <col min="3" max="3" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="18.85546875" customWidth="true"/>
+    <col min="5" max="5" width="8" customWidth="true"/>
+    <col min="6" max="6" width="14.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1123,7 +1129,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B51" s="0">
         <v>0.43619659850972647</v>
@@ -1143,7 +1149,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B52" s="0">
         <v>0.47786073542689311</v>
@@ -1163,7 +1169,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B53" s="0">
         <v>0.48013453345495433</v>
@@ -1183,7 +1189,7 @@
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B54" s="0">
         <v>0.4908782098967594</v>
@@ -1203,7 +1209,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B55" s="0">
         <v>0.49596511762196904</v>
@@ -1223,7 +1229,7 @@
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B56" s="0">
         <v>0.52774250341143503</v>
@@ -1243,7 +1249,7 @@
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B57" s="0">
         <v>0.52911008457025355</v>
@@ -1263,7 +1269,7 @@
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B58" s="0">
         <v>0.53569741663661175</v>
@@ -1283,7 +1289,7 @@
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B59" s="0">
         <v>0.56120296608639531</v>
@@ -1303,7 +1309,7 @@
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B60" s="0">
         <v>0.57659832430495972</v>
@@ -1323,7 +1329,7 @@
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B61" s="0">
         <v>0.61129319437109186</v>
@@ -1343,7 +1349,7 @@
     </row>
     <row r="62">
       <c r="A62" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B62" s="0">
         <v>0.61551105230893688</v>
@@ -1363,7 +1369,7 @@
     </row>
     <row r="63">
       <c r="A63" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B63" s="0">
         <v>0.67203022284910963</v>
@@ -1383,7 +1389,7 @@
     </row>
     <row r="64">
       <c r="A64" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B64" s="0">
         <v>0.67805334778370197</v>
@@ -1403,7 +1409,7 @@
     </row>
     <row r="65">
       <c r="A65" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B65" s="0">
         <v>0.68530716498780331</v>
@@ -1423,7 +1429,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B66" s="0">
         <v>0.72893603477173197</v>
@@ -1443,7 +1449,7 @@
     </row>
     <row r="67">
       <c r="A67" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B67" s="0">
         <v>0.73288962705940852</v>
@@ -1463,7 +1469,7 @@
     </row>
     <row r="68">
       <c r="A68" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B68" s="0">
         <v>0.73552566413155063</v>
@@ -1483,7 +1489,7 @@
     </row>
     <row r="69">
       <c r="A69" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B69" s="0">
         <v>0.73642334446320623</v>
@@ -1503,7 +1509,7 @@
     </row>
     <row r="70">
       <c r="A70" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B70" s="0">
         <v>0.76996381309961448</v>
@@ -1523,7 +1529,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B71" s="0">
         <v>0.77551042610335241</v>
@@ -1543,7 +1549,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B72" s="0">
         <v>0.80725885284094656</v>
@@ -1563,7 +1569,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B73" s="0">
         <v>0.84077811276679315</v>
@@ -1583,7 +1589,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B74" s="0">
         <v>0.93555895867309458</v>
@@ -1603,7 +1609,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B75" s="0">
         <v>0.95077140882833622</v>
@@ -1623,7 +1629,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B76" s="0">
         <v>1</v>
@@ -1643,7 +1649,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B77" s="0">
         <v>1</v>
@@ -1663,7 +1669,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B78" s="0">
         <v>1</v>
@@ -1683,7 +1689,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B79" s="0">
         <v>1</v>
@@ -1703,7 +1709,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B80" s="0">
         <v>1</v>
@@ -1723,7 +1729,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B81" s="0">
         <v>1</v>
@@ -1743,7 +1749,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B82" s="0">
         <v>1</v>
@@ -1763,7 +1769,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B83" s="0">
         <v>1</v>
@@ -1783,7 +1789,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B84" s="0">
         <v>1</v>
@@ -1803,7 +1809,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B85" s="0">
         <v>1</v>
@@ -1823,7 +1829,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B86" s="0">
         <v>1</v>
@@ -1843,7 +1849,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B87" s="0">
         <v>1</v>
@@ -1863,7 +1869,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B88" s="0">
         <v>1</v>
@@ -1883,7 +1889,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B89" s="0">
         <v>1</v>
@@ -1903,7 +1909,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B90" s="0">
         <v>1</v>
@@ -1923,7 +1929,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B91" s="0">
         <v>1</v>
@@ -1943,7 +1949,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B92" s="0">
         <v>1</v>
@@ -1963,7 +1969,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B93" s="0">
         <v>1</v>
@@ -1983,7 +1989,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B94" s="0">
         <v>1</v>
@@ -2003,7 +2009,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B95" s="0">
         <v>1</v>
@@ -2023,7 +2029,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B96" s="0">
         <v>1</v>
@@ -2043,7 +2049,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B97" s="0">
         <v>1</v>
@@ -2063,7 +2069,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B98" s="0">
         <v>1</v>
@@ -2083,7 +2089,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B99" s="0">
         <v>1</v>
@@ -2103,7 +2109,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B100" s="0">
         <v>0.70479692530212534</v>
@@ -2123,7 +2129,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B101" s="0">
         <v>0.76316461128513291</v>
@@ -2143,7 +2149,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B102" s="0">
         <v>0.76631935644878069</v>
@@ -2163,7 +2169,7 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B103" s="0">
         <v>0.78118413563535827</v>
@@ -2183,7 +2189,7 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B104" s="0">
         <v>0.78819876178291781</v>
@@ -2203,7 +2209,7 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B105" s="0">
         <v>0.83168635767218102</v>
@@ -2223,7 +2229,7 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B106" s="0">
         <v>0.83354536659880851</v>
@@ -2243,7 +2249,7 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B107" s="0">
         <v>0.84248566770878097</v>
@@ -2263,7 +2269,7 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B108" s="0">
         <v>0.87688560058725695</v>
@@ -2283,7 +2289,7 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B109" s="0">
         <v>0.89748831109511618</v>
@@ -2303,7 +2309,7 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B110" s="0">
         <v>0.94349339829750212</v>
@@ -2323,7 +2329,7 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B111" s="0">
         <v>0.96729141589180545</v>
@@ -2343,7 +2349,7 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B112" s="0">
         <v>1</v>
@@ -2363,7 +2369,7 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B113" s="0">
         <v>1</v>
@@ -2383,7 +2389,7 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B114" s="0">
         <v>1</v>
@@ -2403,7 +2409,7 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B115" s="0">
         <v>1</v>
@@ -2423,7 +2429,7 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B116" s="0">
         <v>1</v>
@@ -2443,7 +2449,7 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B117" s="0">
         <v>1</v>
@@ -2463,7 +2469,7 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B118" s="0">
         <v>1</v>
@@ -2483,7 +2489,7 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B119" s="0">
         <v>1</v>
@@ -2503,7 +2509,7 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B120" s="0">
         <v>1</v>
@@ -2523,7 +2529,7 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B121" s="0">
         <v>1</v>
@@ -2543,7 +2549,7 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B122" s="0">
         <v>1</v>
@@ -2563,7 +2569,7 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B123" s="0">
         <v>1</v>
@@ -2583,7 +2589,7 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B124" s="0">
         <v>1</v>
@@ -2603,7 +2609,7 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B125" s="0">
         <v>1</v>
@@ -2623,7 +2629,7 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B126" s="0">
         <v>1</v>
@@ -2643,7 +2649,7 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B127" s="0">
         <v>1</v>
@@ -2663,7 +2669,7 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B128" s="0">
         <v>1</v>
@@ -2683,7 +2689,7 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B129" s="0">
         <v>1</v>
@@ -2703,7 +2709,7 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B130" s="0">
         <v>1</v>
@@ -2723,7 +2729,7 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B131" s="0">
         <v>1</v>
@@ -2743,7 +2749,7 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B132" s="0">
         <v>1</v>
@@ -2763,7 +2769,7 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B133" s="0">
         <v>1</v>
@@ -2783,7 +2789,7 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B134" s="0">
         <v>1</v>
@@ -2803,7 +2809,7 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B135" s="0">
         <v>1</v>
@@ -2823,7 +2829,7 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B136" s="0">
         <v>1</v>
@@ -2843,7 +2849,7 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B137" s="0">
         <v>1</v>
@@ -2863,7 +2869,7 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B138" s="0">
         <v>1</v>
@@ -2883,7 +2889,7 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B139" s="0">
         <v>1</v>
@@ -2903,7 +2909,7 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B140" s="0">
         <v>1</v>
@@ -2923,7 +2929,7 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B141" s="0">
         <v>1</v>
@@ -2943,7 +2949,7 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B142" s="0">
         <v>1</v>
@@ -2963,7 +2969,7 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B143" s="0">
         <v>1</v>
@@ -2983,7 +2989,7 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B144" s="0">
         <v>1</v>
@@ -3003,7 +3009,7 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B145" s="0">
         <v>1</v>
@@ -3023,7 +3029,7 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B146" s="0">
         <v>1</v>
@@ -3043,7 +3049,7 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B147" s="0">
         <v>1</v>
@@ -3063,7 +3069,7 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B148" s="0">
         <v>1</v>
@@ -3090,16 +3096,16 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.21875" customWidth="true"/>
-    <col min="2" max="2" width="7.21875" customWidth="true"/>
-    <col min="3" max="3" width="9.44140625" customWidth="true"/>
-    <col min="4" max="4" width="14.21875" customWidth="true"/>
-    <col min="5" max="5" width="17.44140625" customWidth="true"/>
-    <col min="6" max="6" width="20.77734375" customWidth="true"/>
-    <col min="7" max="7" width="21.5546875" customWidth="true"/>
-    <col min="8" max="8" width="14.88671875" customWidth="true"/>
-    <col min="9" max="9" width="18.5546875" customWidth="true"/>
-    <col min="10" max="10" width="13.5546875" customWidth="true"/>
+    <col min="1" max="1" width="9.28515625" customWidth="true"/>
+    <col min="2" max="2" width="8" customWidth="true"/>
+    <col min="3" max="3" width="10.28515625" customWidth="true"/>
+    <col min="4" max="4" width="15.28515625" customWidth="true"/>
+    <col min="5" max="5" width="19" customWidth="true"/>
+    <col min="6" max="6" width="22" customWidth="true"/>
+    <col min="7" max="7" width="22.85546875" customWidth="true"/>
+    <col min="8" max="8" width="16" customWidth="true"/>
+    <col min="9" max="9" width="18.85546875" customWidth="true"/>
+    <col min="10" max="10" width="14.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3168,7 +3174,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" s="0">
         <v>49</v>
@@ -3200,7 +3206,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B4" s="0">
         <v>49</v>
